--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_47.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5712247.794390502</v>
+        <v>5672221.701637109</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645784</v>
+        <v>6767152.318645786</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645784</v>
+        <v>6767152.318645786</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517484</v>
+        <v>2916902.906517461</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517484</v>
+        <v>2916902.906517461</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38028734.44626995</v>
+        <v>38028734.44626997</v>
       </c>
     </row>
   </sheetData>
@@ -672,43 +672,43 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>408.0096587035274</v>
+        <v>250.7004512606472</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
+        <v>97.12488247690067</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>708.6062368062544</v>
+      </c>
+      <c r="N2" t="n">
         <v>814</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>814</v>
-      </c>
-      <c r="N2" t="n">
-        <v>194.5855355810472</v>
-      </c>
-      <c r="O2" t="n">
-        <v>611.1455837021077</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>530.163813431294</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -717,13 +717,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>118.0893820455457</v>
+        <v>125.5575371970017</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>297.3920501269283</v>
+        <v>297.3920501269251</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
         <v>3.75737228701621</v>
@@ -918,34 +918,34 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690061</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L5" t="n">
+        <v>216.0296191332224</v>
+      </c>
+      <c r="M5" t="n">
+        <v>297.9910820919849</v>
+      </c>
+      <c r="N5" t="n">
+        <v>194.5855355810472</v>
+      </c>
+      <c r="O5" t="n">
         <v>814</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>814</v>
-      </c>
-      <c r="N5" t="n">
-        <v>708.6062368062543</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>438.3363995050528</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>586.6755817285639</v>
+        <v>279.285214602999</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>63.0833896009366</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061046</v>
+        <v>114.9691617060972</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>174.6089458300097</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>96.36700516145139</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,13 +1155,13 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690067</v>
+        <v>313.1545016101224</v>
       </c>
       <c r="L8" t="n">
-        <v>87.18991228311896</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
-        <v>814</v>
+        <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
         <v>194.5855355810472</v>
@@ -1173,16 +1173,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>797.8013999999999</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1194,7 +1194,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>511.3174326828064</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>147.2737972923793</v>
+        <v>243.8995092302829</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
@@ -1267,10 +1267,10 @@
         <v>400.2103597601867</v>
       </c>
       <c r="V9" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>90.09876729325129</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.3920501269237</v>
+        <v>297.3920501269269</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>30.99877799317735</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
         <v>179.8896287080119</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,13 +1413,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>236.8601719068449</v>
       </c>
       <c r="U11" t="n">
         <v>424.2212965486107</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>340.7767994885277</v>
+        <v>203.4033197856722</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1605,22 +1605,22 @@
         <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>112.1646315222934</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D14" t="n">
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>71.22605108397006</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>59.47050485464629</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>53.74128073011011</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -1902,7 +1902,7 @@
         <v>350.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>359.3734759809475</v>
+        <v>358.9428673663618</v>
       </c>
       <c r="X17" t="n">
         <v>313.2818334606677</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>339.4016293563777</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>125.4590200934258</v>
+        <v>125.4590200934799</v>
       </c>
       <c r="G20" t="n">
         <v>124.7573722870162</v>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>377.7929984536983</v>
+        <v>329.1179939996816</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.4175591877372</v>
+        <v>215.4175591878056</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2498,28 +2498,28 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>96.37490231186223</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>338.6387678008247</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>6.402017141860561</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>25.06186612413871</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>404.8510241668239</v>
@@ -2738,13 +2738,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>45.14518808597777</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2787,25 +2787,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>51.6325347058354</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>389.1583941510048</v>
       </c>
       <c r="V29" t="n">
         <v>404.8510241668239</v>
@@ -2856,7 +2856,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -3036,7 +3036,7 @@
         <v>113.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>122.3462200934261</v>
+        <v>113.8896287080119</v>
       </c>
       <c r="G32" t="n">
         <v>112.7573722870162</v>
@@ -3048,19 +3048,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589747</v>
+        <v>757.6173000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320763039</v>
+        <v>10.23281455290589</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920259</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810884</v>
+        <v>717.6337696749089</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>727.6783648198339</v>
+        <v>757.6173000000409</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="33">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3221,16 +3221,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>70.05053078766994</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>62.05083562932418</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3285,31 +3285,31 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.738269658982</v>
+        <v>377.7382696589829</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320762842</v>
+        <v>10.23281455290589</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>256.9910820920331</v>
+        <v>256.991082092034</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810957</v>
+        <v>153.5855355810966</v>
       </c>
       <c r="O35" t="n">
-        <v>397.7077537618954</v>
+        <v>702.3188823428662</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.9706110579601</v>
+        <v>742.2346000000472</v>
       </c>
       <c r="R35" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>203.8481678023229</v>
@@ -3330,7 +3330,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="36">
@@ -3464,13 +3464,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>433.5163175103893</v>
       </c>
       <c r="R37" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>70.05053078767008</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>190.9993129555745</v>
+        <v>199.4559043409888</v>
       </c>
       <c r="C38" t="n">
         <v>158.4745782429939</v>
@@ -3516,34 +3516,34 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H38" t="n">
-        <v>125.4662500889416</v>
+        <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589893</v>
+        <v>377.7382696589902</v>
       </c>
       <c r="K38" t="n">
-        <v>56.12488247690067</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>449.2763389422919</v>
+        <v>351.8156858378637</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920404</v>
+        <v>256.9910820920413</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000557</v>
+        <v>153.5855355811038</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.9706110579674</v>
+        <v>329.9706110579683</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3698,16 +3698,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q40" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>37.83128173769168</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>187.8394798201826</v>
       </c>
       <c r="D41" t="n">
-        <v>107.7770918895001</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
         <v>281.8481678023229</v>
@@ -3795,7 +3795,7 @@
         <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>425.3734759809475</v>
@@ -3804,7 +3804,7 @@
         <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3832,7 +3832,7 @@
         <v>112.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>119.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>4.126385891348534</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>85.20519297838521</v>
+        <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>253.5639999646113</v>
+        <v>235.2656444087128</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>197.1638187766239</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>56.42465610346201</v>
       </c>
       <c r="C44" t="n">
         <v>262.4745782429939</v>
@@ -3981,16 +3981,16 @@
         <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>199.4236251809434</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
@@ -4035,7 +4035,7 @@
         <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
         <v>405.2818334606677</v>
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27.59675859191825</v>
+        <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>30.12638589134853</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>360.2737972923793</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>16.55705513387049</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4184,16 +4184,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>702.4077201726793</v>
+        <v>391.9123998438258</v>
       </c>
       <c r="C2" t="n">
-        <v>652.4333987151097</v>
+        <v>341.9380783862562</v>
       </c>
       <c r="D2" t="n">
-        <v>641.9898070586958</v>
+        <v>331.4944867298423</v>
       </c>
       <c r="E2" t="n">
-        <v>637.5824438194345</v>
+        <v>327.0871234905811</v>
       </c>
       <c r="F2" t="n">
-        <v>632.6434249224528</v>
+        <v>322.1481045935994</v>
       </c>
       <c r="G2" t="n">
-        <v>628.8480993800122</v>
+        <v>318.3527790511588</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
@@ -4324,19 +4324,19 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>431.6498286273397</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L2" t="n">
-        <v>1237.50982862734</v>
+        <v>1961.626108953703</v>
       </c>
       <c r="M2" t="n">
-        <v>1221.147606405118</v>
+        <v>2051.72223339183</v>
       </c>
       <c r="N2" t="n">
-        <v>1830.456560363656</v>
+        <v>2035.360011169607</v>
       </c>
       <c r="O2" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P2" t="n">
         <v>2824.857788947385</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3160.193769896644</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2624.67476643069</v>
+        <v>1910.139042061433</v>
       </c>
       <c r="U2" t="n">
-        <v>2372.936083048255</v>
+        <v>1658.400358678998</v>
       </c>
       <c r="V2" t="n">
-        <v>2140.763331364595</v>
+        <v>1426.227606995337</v>
       </c>
       <c r="W2" t="n">
-        <v>1899.982042494951</v>
+        <v>781.4059140852892</v>
       </c>
       <c r="X2" t="n">
-        <v>1301.717564251852</v>
+        <v>587.1818398825944</v>
       </c>
       <c r="Y2" t="n">
-        <v>785.2353090166939</v>
+        <v>474.7399886878405</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2562.916695170275</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="C3" t="n">
-        <v>2562.916695170275</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="D3" t="n">
-        <v>2562.916695170275</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="E3" t="n">
-        <v>2562.916695170275</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="F3" t="n">
-        <v>2219.849783717874</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="G3" t="n">
-        <v>2219.849783717874</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="H3" t="n">
-        <v>2219.849783717874</v>
+        <v>191.9457951484865</v>
       </c>
       <c r="I3" t="n">
-        <v>2100.567579631464</v>
+        <v>65.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2224.524099806763</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>2413.716915901147</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>2685.067377496347</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M3" t="n">
-        <v>2771.147919239206</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>2904.428203846775</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O3" t="n">
-        <v>3143.470655530493</v>
+        <v>1108.023075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>3107.238588593556</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>3040.002224992939</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>3034.590340934844</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>2630.33745228819</v>
+        <v>594.8898726567263</v>
       </c>
       <c r="V3" t="n">
-        <v>2615.680212700796</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W3" t="n">
-        <v>2582.980068347434</v>
+        <v>547.5324887159701</v>
       </c>
       <c r="X3" t="n">
-        <v>2562.916695170275</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="Y3" t="n">
-        <v>2562.916695170275</v>
+        <v>527.4691155388109</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2170.256671467609</v>
+        <v>218.923467772069</v>
       </c>
       <c r="C4" t="n">
-        <v>2296.258677286045</v>
+        <v>344.9254735905048</v>
       </c>
       <c r="D4" t="n">
-        <v>2409.577821411045</v>
+        <v>458.2446177155049</v>
       </c>
       <c r="E4" t="n">
-        <v>2527.406725622458</v>
+        <v>576.0735219269179</v>
       </c>
       <c r="F4" t="n">
-        <v>2651.767698214393</v>
+        <v>700.4344945188534</v>
       </c>
       <c r="G4" t="n">
-        <v>2805.174264101278</v>
+        <v>853.8410604057386</v>
       </c>
       <c r="H4" t="n">
-        <v>2974.690849260676</v>
+        <v>853.8410604057386</v>
       </c>
       <c r="I4" t="n">
-        <v>3145.635566063132</v>
+        <v>1074.973939341822</v>
       </c>
       <c r="J4" t="n">
-        <v>3145.635566063132</v>
+        <v>1436.057679994273</v>
       </c>
       <c r="K4" t="n">
-        <v>3256</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L4" t="n">
-        <v>3232.214517012344</v>
+        <v>1522.636630943485</v>
       </c>
       <c r="M4" t="n">
-        <v>3110.364404484516</v>
+        <v>1400.786518415657</v>
       </c>
       <c r="N4" t="n">
-        <v>2937.45018703837</v>
+        <v>1227.872300969511</v>
       </c>
       <c r="O4" t="n">
-        <v>2694.57587988785</v>
+        <v>984.9979938189905</v>
       </c>
       <c r="P4" t="n">
-        <v>2404.224468445146</v>
+        <v>694.646582376286</v>
       </c>
       <c r="Q4" t="n">
-        <v>2075.093896298077</v>
+        <v>365.5160102292173</v>
       </c>
       <c r="R4" t="n">
-        <v>1774.697886068857</v>
+        <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1811.94814116303</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>1811.94814116303</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>2058.499333801316</v>
+        <v>107.1661301057769</v>
       </c>
       <c r="V4" t="n">
-        <v>2058.499333801316</v>
+        <v>107.1661301057769</v>
       </c>
       <c r="W4" t="n">
-        <v>2058.499333801316</v>
+        <v>107.1661301057769</v>
       </c>
       <c r="X4" t="n">
-        <v>2058.499333801316</v>
+        <v>107.1661301057769</v>
       </c>
       <c r="Y4" t="n">
-        <v>2058.499333801316</v>
+        <v>107.1661301057769</v>
       </c>
     </row>
     <row r="5">
@@ -4534,16 +4534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>702.4077201726793</v>
+        <v>1106.448124213083</v>
       </c>
       <c r="C5" t="n">
-        <v>652.4333987151097</v>
+        <v>1056.473802755514</v>
       </c>
       <c r="D5" t="n">
-        <v>641.9898070586958</v>
+        <v>1046.0302110991</v>
       </c>
       <c r="E5" t="n">
-        <v>637.5824438194345</v>
+        <v>1041.622847859839</v>
       </c>
       <c r="F5" t="n">
         <v>632.6434249224528</v>
@@ -4564,16 +4564,16 @@
         <v>1155.766108953703</v>
       </c>
       <c r="L5" t="n">
-        <v>1139.40388673148</v>
+        <v>1743.414372455498</v>
       </c>
       <c r="M5" t="n">
-        <v>1123.041664509258</v>
+        <v>2248.273279433291</v>
       </c>
       <c r="N5" t="n">
-        <v>1213.137788947385</v>
+        <v>2857.58223339183</v>
       </c>
       <c r="O5" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P5" t="n">
         <v>2824.857788947385</v>
@@ -4582,10 +4582,10 @@
         <v>3256</v>
       </c>
       <c r="R5" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2813.235960095906</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T5" t="n">
         <v>2220.634362390286</v>
@@ -4600,10 +4600,10 @@
         <v>1495.941638454547</v>
       </c>
       <c r="X5" t="n">
-        <v>897.6771602114478</v>
+        <v>1301.717564251852</v>
       </c>
       <c r="Y5" t="n">
-        <v>785.2353090166939</v>
+        <v>1189.275713057098</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>65.12</v>
+        <v>754.3203429896864</v>
       </c>
       <c r="E6" t="n">
-        <v>65.12</v>
+        <v>408.1869114524009</v>
       </c>
       <c r="F6" t="n">
         <v>65.12</v>
@@ -4661,28 +4661,28 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>667.7506049216878</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>600.5142413210704</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>536.7936457645687</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>132.5407571179154</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>117.8835175305213</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>85.18337317715914</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,37 +4692,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>410.4906232651239</v>
+        <v>401.9611933528821</v>
       </c>
       <c r="C7" t="n">
-        <v>536.4926290835597</v>
+        <v>527.9631991713179</v>
       </c>
       <c r="D7" t="n">
-        <v>649.8117732085598</v>
+        <v>641.282343296318</v>
       </c>
       <c r="E7" t="n">
-        <v>767.6406774199728</v>
+        <v>641.282343296318</v>
       </c>
       <c r="F7" t="n">
-        <v>892.0016500119083</v>
+        <v>641.282343296318</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.408215898794</v>
+        <v>794.6889091832032</v>
       </c>
       <c r="H7" t="n">
-        <v>1214.924801058191</v>
+        <v>964.2054943426008</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994274</v>
+        <v>1185.338373278684</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994274</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="M7" t="n">
         <v>1430.29164756134</v>
@@ -4743,25 +4743,25 @@
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>65.12</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>253.1956791588049</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>253.1956791588049</v>
+        <v>290.445934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>298.7332855988318</v>
+        <v>290.445934252978</v>
       </c>
       <c r="W7" t="n">
-        <v>298.7332855988318</v>
+        <v>290.445934252978</v>
       </c>
       <c r="X7" t="n">
-        <v>298.7332855988318</v>
+        <v>290.445934252978</v>
       </c>
       <c r="Y7" t="n">
-        <v>298.7332855988318</v>
+        <v>290.445934252978</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>702.4077201726793</v>
+        <v>391.9123998438259</v>
       </c>
       <c r="C8" t="n">
-        <v>652.4333987151097</v>
+        <v>341.9380783862563</v>
       </c>
       <c r="D8" t="n">
-        <v>641.9898070586958</v>
+        <v>331.4944867298424</v>
       </c>
       <c r="E8" t="n">
-        <v>637.5824438194345</v>
+        <v>327.0871234905811</v>
       </c>
       <c r="F8" t="n">
-        <v>632.6434249224528</v>
+        <v>322.1481045935994</v>
       </c>
       <c r="G8" t="n">
-        <v>628.8480993800122</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4798,22 +4798,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>1155.766108953703</v>
+        <v>937.554372455499</v>
       </c>
       <c r="L8" t="n">
-        <v>1873.555490485906</v>
+        <v>921.1921502332766</v>
       </c>
       <c r="M8" t="n">
-        <v>1857.193268263684</v>
+        <v>1426.05105721107</v>
       </c>
       <c r="N8" t="n">
-        <v>2466.502222222222</v>
+        <v>2035.360011169608</v>
       </c>
       <c r="O8" t="n">
-        <v>2450.14</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P8" t="n">
-        <v>3256</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
@@ -4822,25 +4822,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>2906.781043807457</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T8" t="n">
-        <v>2718.219850142241</v>
+        <v>1910.139042061433</v>
       </c>
       <c r="U8" t="n">
-        <v>2466.481166759806</v>
+        <v>1658.400358678998</v>
       </c>
       <c r="V8" t="n">
-        <v>2234.308415076146</v>
+        <v>1426.227606995337</v>
       </c>
       <c r="W8" t="n">
-        <v>1993.527126206502</v>
+        <v>1185.446318125693</v>
       </c>
       <c r="X8" t="n">
-        <v>1395.262647963403</v>
+        <v>991.2222439229986</v>
       </c>
       <c r="Y8" t="n">
-        <v>878.7803927282447</v>
+        <v>474.7399886878405</v>
       </c>
     </row>
     <row r="9">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C9" t="n">
         <v>65.12</v>
@@ -4898,28 +4898,28 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1071.791008962092</v>
+        <v>974.1892797318862</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.554645361474</v>
+        <v>906.9529161312688</v>
       </c>
       <c r="T9" t="n">
-        <v>999.1427613033796</v>
+        <v>901.5410320731741</v>
       </c>
       <c r="U9" t="n">
-        <v>594.8898726567263</v>
+        <v>497.2881434265207</v>
       </c>
       <c r="V9" t="n">
-        <v>176.1922290289281</v>
+        <v>482.6309038391266</v>
       </c>
       <c r="W9" t="n">
-        <v>85.18337317715914</v>
+        <v>449.9307594857645</v>
       </c>
       <c r="X9" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y9" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>410.4906232651212</v>
+        <v>836.5342818821732</v>
       </c>
       <c r="C10" t="n">
-        <v>536.4926290835569</v>
+        <v>836.5342818821732</v>
       </c>
       <c r="D10" t="n">
-        <v>649.811773208557</v>
+        <v>836.5342818821732</v>
       </c>
       <c r="E10" t="n">
-        <v>767.6406774199701</v>
+        <v>954.3631860935863</v>
       </c>
       <c r="F10" t="n">
-        <v>892.0016500119056</v>
+        <v>1078.724158685522</v>
       </c>
       <c r="G10" t="n">
-        <v>1045.408215898791</v>
+        <v>1232.130724572407</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058188</v>
+        <v>1401.647309731805</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994271</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994271</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943484</v>
+        <v>1522.636630943487</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415656</v>
+        <v>1400.786518415659</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.872300969509</v>
+        <v>1227.872300969512</v>
       </c>
       <c r="O10" t="n">
-        <v>984.9979938189891</v>
+        <v>984.9979938189923</v>
       </c>
       <c r="P10" t="n">
-        <v>694.6465823762846</v>
+        <v>694.6465823762878</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292159</v>
+        <v>365.5160102292191</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
@@ -4992,13 +4992,13 @@
         <v>290.445934252978</v>
       </c>
       <c r="W10" t="n">
-        <v>290.445934252978</v>
+        <v>462.3368525126554</v>
       </c>
       <c r="X10" t="n">
-        <v>290.445934252978</v>
+        <v>613.3676435368488</v>
       </c>
       <c r="Y10" t="n">
-        <v>298.7332855988291</v>
+        <v>724.7769442158811</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>689.7388319673844</v>
+        <v>841.9550023209335</v>
       </c>
       <c r="C11" t="n">
-        <v>462.996833742138</v>
+        <v>615.2130040956872</v>
       </c>
       <c r="D11" t="n">
-        <v>462.996833742138</v>
+        <v>428.0017356715965</v>
       </c>
       <c r="E11" t="n">
-        <v>431.6849367793326</v>
+        <v>246.8266956646584</v>
       </c>
       <c r="F11" t="n">
-        <v>249.9782411146742</v>
+        <v>65.12</v>
       </c>
       <c r="G11" t="n">
-        <v>249.9782411146742</v>
+        <v>65.12</v>
       </c>
       <c r="H11" t="n">
         <v>65.12</v>
@@ -5038,16 +5038,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>1262.289113037656</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>1262.289113037656</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N11" t="n">
-        <v>1875.509432812419</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O11" t="n">
-        <v>2681.369432812419</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="P11" t="n">
         <v>2817.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3229.860001183541</v>
+        <v>3256</v>
       </c>
       <c r="S11" t="n">
-        <v>3229.860001183541</v>
+        <v>3256</v>
       </c>
       <c r="T11" t="n">
-        <v>2864.531130750648</v>
+        <v>3016.747301104197</v>
       </c>
       <c r="U11" t="n">
-        <v>2436.024770600536</v>
+        <v>2588.240940954085</v>
       </c>
       <c r="V11" t="n">
-        <v>2027.084342149199</v>
+        <v>2179.300512502748</v>
       </c>
       <c r="W11" t="n">
-        <v>1609.535376511878</v>
+        <v>1761.751546865427</v>
       </c>
       <c r="X11" t="n">
-        <v>1238.543625541507</v>
+        <v>1390.759795895056</v>
       </c>
       <c r="Y11" t="n">
-        <v>949.3340975790759</v>
+        <v>1101.550267932625</v>
       </c>
     </row>
     <row r="12">
@@ -5111,22 +5111,22 @@
         <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>419.6213981428639</v>
+        <v>215.7971006891144</v>
       </c>
       <c r="K12" t="n">
-        <v>831.5642142372474</v>
+        <v>627.7399167834978</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.664675832448</v>
+        <v>1121.840378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.495217575307</v>
+        <v>1430.670920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>1990.525502182875</v>
+        <v>1786.701204729125</v>
       </c>
       <c r="O12" t="n">
-        <v>2452.317953866594</v>
+        <v>2248.493656412844</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5214,7 +5214,7 @@
         <v>409.3389893823512</v>
       </c>
       <c r="R13" t="n">
-        <v>65.12</v>
+        <v>203.8810906089449</v>
       </c>
       <c r="S13" t="n">
         <v>65.12</v>
@@ -5248,19 +5248,19 @@
         <v>653.4059340138207</v>
       </c>
       <c r="C14" t="n">
-        <v>540.1083264155445</v>
+        <v>452.9265620512006</v>
       </c>
       <c r="D14" t="n">
-        <v>379.1596842540801</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>379.1596842540801</v>
+        <v>137.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>223.7156148520479</v>
+        <v>65.12</v>
       </c>
       <c r="G14" t="n">
-        <v>223.7156148520479</v>
+        <v>65.12</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5269,22 +5269,22 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>81.61175644363402</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.135479385524</v>
+        <v>81.61175644363402</v>
       </c>
       <c r="L14" t="n">
-        <v>1693.331756443634</v>
+        <v>81.61175644363402</v>
       </c>
       <c r="M14" t="n">
-        <v>2204.180585172569</v>
+        <v>592.460585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>2817.400904947332</v>
+        <v>1205.680904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P14" t="n">
         <v>2817.400904947332</v>
@@ -5351,22 +5351,22 @@
         <v>222.6113981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>660.2942142372473</v>
+        <v>411.8042142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>1096.180984439304</v>
+        <v>931.6446758324474</v>
       </c>
       <c r="M15" t="n">
-        <v>1430.751526182163</v>
+        <v>1266.215217575307</v>
       </c>
       <c r="N15" t="n">
-        <v>1564.031810789731</v>
+        <v>1647.985502182875</v>
       </c>
       <c r="O15" t="n">
-        <v>2051.564262473451</v>
+        <v>1887.027953866594</v>
       </c>
       <c r="P15" t="n">
-        <v>2164.093606942957</v>
+        <v>2241.235134503383</v>
       </c>
       <c r="Q15" t="n">
         <v>2241.235134503383</v>
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.9399739669084</v>
+        <v>210.6276980209074</v>
       </c>
       <c r="C16" t="n">
-        <v>283.9399739669084</v>
+        <v>188.6830044370238</v>
       </c>
       <c r="D16" t="n">
-        <v>283.9399739669084</v>
+        <v>188.6830044370238</v>
       </c>
       <c r="E16" t="n">
-        <v>283.9399739669084</v>
+        <v>158.3992621774718</v>
       </c>
       <c r="F16" t="n">
-        <v>283.9399739669084</v>
+        <v>134.7802157454092</v>
       </c>
       <c r="G16" t="n">
-        <v>289.8365398537936</v>
+        <v>140.6767816322945</v>
       </c>
       <c r="H16" t="n">
-        <v>311.8431250131912</v>
+        <v>162.683366791692</v>
       </c>
       <c r="I16" t="n">
-        <v>385.4660039492741</v>
+        <v>236.306245727775</v>
       </c>
       <c r="J16" t="n">
-        <v>599.0397446017254</v>
+        <v>449.8799863802262</v>
       </c>
       <c r="K16" t="n">
-        <v>599.0397446017254</v>
+        <v>411.9802148639201</v>
       </c>
       <c r="L16" t="n">
-        <v>599.0397446017254</v>
+        <v>237.6896813712139</v>
       </c>
       <c r="M16" t="n">
-        <v>599.0397446017254</v>
+        <v>177.6184643463186</v>
       </c>
       <c r="N16" t="n">
-        <v>599.0397446017254</v>
+        <v>177.6184643463186</v>
       </c>
       <c r="O16" t="n">
-        <v>599.0397446017254</v>
+        <v>177.6184643463186</v>
       </c>
       <c r="P16" t="n">
-        <v>544.7556226521192</v>
+        <v>177.6184643463186</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.12</v>
+        <v>177.6184643463186</v>
       </c>
       <c r="R16" t="n">
-        <v>65.12</v>
+        <v>177.6184643463186</v>
       </c>
       <c r="S16" t="n">
         <v>65.12</v>
@@ -5472,7 +5472,7 @@
         <v>283.9399739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>283.9399739669084</v>
+        <v>247.1062842199767</v>
       </c>
     </row>
     <row r="17">
@@ -5506,22 +5506,22 @@
         <v>65.12</v>
       </c>
       <c r="J17" t="n">
-        <v>65.12</v>
+        <v>81.61175644363432</v>
       </c>
       <c r="K17" t="n">
-        <v>774.8263663478684</v>
+        <v>81.61175644363432</v>
       </c>
       <c r="L17" t="n">
-        <v>1580.686366347868</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M17" t="n">
-        <v>2091.535195076804</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>2704.755514851567</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>2704.755514851567</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>2817.400904947332</v>
@@ -5533,16 +5533,16 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W17" t="n">
         <v>1636.263699381128</v>
@@ -5594,16 +5594,16 @@
         <v>987.0846758324474</v>
       </c>
       <c r="M18" t="n">
-        <v>1073.165217575307</v>
+        <v>1332.140629500164</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.559386547307</v>
+        <v>1465.420914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5682,10 +5682,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3027230120967</v>
+        <v>446.72908934717</v>
       </c>
       <c r="Q19" t="n">
-        <v>407.9499286428058</v>
+        <v>446.72908934717</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>879.6685602764463</v>
+        <v>879.6685602765009</v>
       </c>
       <c r="C20" t="n">
-        <v>707.4720165966545</v>
+        <v>707.4720165967091</v>
       </c>
       <c r="D20" t="n">
-        <v>574.8062027180183</v>
+        <v>574.8062027180729</v>
       </c>
       <c r="E20" t="n">
-        <v>448.1766172565348</v>
+        <v>448.1766172565894</v>
       </c>
       <c r="F20" t="n">
         <v>321.4503343338824</v>
@@ -5746,19 +5746,19 @@
         <v>65.12</v>
       </c>
       <c r="K20" t="n">
-        <v>81.61175644363432</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L20" t="n">
-        <v>887.4717564436343</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M20" t="n">
-        <v>1398.320585172569</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N20" t="n">
-        <v>2011.540904947332</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O20" t="n">
-        <v>2011.540904947332</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="P20" t="n">
         <v>2817.400904947332</v>
@@ -5767,28 +5767,28 @@
         <v>3256</v>
       </c>
       <c r="R20" t="n">
-        <v>3256</v>
+        <v>3256.000000000055</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3037.971547674476</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.188131787037</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.22722618238</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1998.832252276497</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1635.828741184631</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.382444759714</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342683</v>
+        <v>1084.718371342738</v>
       </c>
     </row>
     <row r="21">
@@ -5819,28 +5819,28 @@
         <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>126.374877967565</v>
+        <v>109.1402898924221</v>
       </c>
       <c r="J21" t="n">
-        <v>526.5413981428638</v>
+        <v>233.0968100677211</v>
       </c>
       <c r="K21" t="n">
-        <v>869.8480986016793</v>
+        <v>422.2896261621045</v>
       </c>
       <c r="L21" t="n">
-        <v>1141.198560196879</v>
+        <v>969.8500877573047</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.279101939739</v>
+        <v>1332.140629500164</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>1465.420914107732</v>
       </c>
       <c r="O21" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P21" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q21" t="n">
         <v>1816.992710260958</v>
@@ -5904,25 +5904,25 @@
         <v>859.3027230120967</v>
       </c>
       <c r="K22" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="L22" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="M22" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="N22" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="O22" t="n">
-        <v>859.3027230120967</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="P22" t="n">
-        <v>446.72908934717</v>
+        <v>849.6857797786189</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5983,13 +5983,13 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>456.4291130376557</v>
+        <v>694.8320762183973</v>
       </c>
       <c r="L23" t="n">
-        <v>887.4717564436343</v>
+        <v>1500.692076218397</v>
       </c>
       <c r="M23" t="n">
-        <v>1398.320585172569</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="N23" t="n">
         <v>2011.540904947332</v>
@@ -6004,7 +6004,7 @@
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256</v>
+        <v>3256.000000000069</v>
       </c>
       <c r="S23" t="n">
         <v>3038.406505870973</v>
@@ -6056,28 +6056,28 @@
         <v>65.12</v>
       </c>
       <c r="I24" t="n">
-        <v>126.374877967565</v>
+        <v>109.1402898924222</v>
       </c>
       <c r="J24" t="n">
-        <v>250.3313981428639</v>
+        <v>233.0968100677211</v>
       </c>
       <c r="K24" t="n">
-        <v>439.5242142372473</v>
+        <v>422.2896261621045</v>
       </c>
       <c r="L24" t="n">
-        <v>864.9885601968795</v>
+        <v>693.6400877573046</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.279101939739</v>
+        <v>1055.930629500164</v>
       </c>
       <c r="N24" t="n">
-        <v>1360.559386547307</v>
+        <v>1189.210914107732</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P24" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q24" t="n">
         <v>1816.992710260958</v>
@@ -6123,43 +6123,43 @@
         <v>428.7519797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>428.7519797853442</v>
+        <v>426.7510658086204</v>
       </c>
       <c r="F25" t="n">
-        <v>433.3229523772797</v>
+        <v>431.3220384005559</v>
       </c>
       <c r="G25" t="n">
-        <v>466.939518264165</v>
+        <v>464.9386042874412</v>
       </c>
       <c r="H25" t="n">
-        <v>516.6661034235625</v>
+        <v>514.6651894468388</v>
       </c>
       <c r="I25" t="n">
-        <v>618.0089823596454</v>
+        <v>616.0080683829217</v>
       </c>
       <c r="J25" t="n">
-        <v>859.3027230120967</v>
+        <v>857.301809035373</v>
       </c>
       <c r="K25" t="n">
-        <v>859.3027230120967</v>
+        <v>847.6848658018952</v>
       </c>
       <c r="L25" t="n">
-        <v>859.3027230120967</v>
+        <v>701.6771605920172</v>
       </c>
       <c r="M25" t="n">
-        <v>859.3027230120967</v>
+        <v>457.6048258419668</v>
       </c>
       <c r="N25" t="n">
-        <v>859.3027230120967</v>
+        <v>162.4683861735982</v>
       </c>
       <c r="O25" t="n">
-        <v>859.3027230120967</v>
+        <v>65.12</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3027230120967</v>
+        <v>65.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>656.3562689594545</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="C26" t="n">
-        <v>429.6142707342081</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="D26" t="n">
-        <v>242.4030023101174</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="E26" t="n">
-        <v>242.4030023101174</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="F26" t="n">
-        <v>242.4030023101174</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="G26" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6223,19 +6223,19 @@
         <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1162.855479385524</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>1162.855479385524</v>
+        <v>2438.974308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>1162.855479385524</v>
+        <v>3052.194627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>1888.130904947306</v>
+        <v>3092</v>
       </c>
       <c r="P26" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q26" t="n">
         <v>3092</v>
@@ -6250,19 +6250,19 @@
         <v>2427.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2402.642207592606</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1993.701779141269</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1576.152813503948</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1205.161062533577</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>915.9515345711459</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6299,13 +6299,13 @@
         <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>828.2842142372474</v>
+        <v>624.4599167834981</v>
       </c>
       <c r="L27" t="n">
-        <v>1322.384675832448</v>
+        <v>1118.560378378698</v>
       </c>
       <c r="M27" t="n">
-        <v>1631.215217575307</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N27" t="n">
         <v>1783.421204729126</v>
@@ -6381,10 +6381,10 @@
         <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>406.0589893823512</v>
+        <v>360.457789295505</v>
       </c>
       <c r="M28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="N28" t="n">
         <v>61.84</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1022.389550081067</v>
+        <v>288.5819982252464</v>
       </c>
       <c r="C29" t="n">
-        <v>795.6475518558203</v>
+        <v>61.84</v>
       </c>
       <c r="D29" t="n">
-        <v>608.4362834317296</v>
+        <v>61.84</v>
       </c>
       <c r="E29" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="F29" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="G29" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6457,19 +6457,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M29" t="n">
-        <v>1673.704308114459</v>
+        <v>509.6405851725002</v>
       </c>
       <c r="N29" t="n">
-        <v>2286.924627889222</v>
+        <v>1122.860904947263</v>
       </c>
       <c r="O29" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947298</v>
       </c>
       <c r="P29" t="n">
         <v>2653.400904947332</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3065.860001183541</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>2700.531130750648</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2272.024770600536</v>
+        <v>2034.867936858398</v>
       </c>
       <c r="V29" t="n">
-        <v>1863.084342149199</v>
+        <v>1625.927508407061</v>
       </c>
       <c r="W29" t="n">
-        <v>1445.535376511878</v>
+        <v>1208.37854276974</v>
       </c>
       <c r="X29" t="n">
-        <v>1074.543625541507</v>
+        <v>837.3867917993684</v>
       </c>
       <c r="Y29" t="n">
-        <v>1074.543625541507</v>
+        <v>548.1772638369378</v>
       </c>
     </row>
     <row r="30">
@@ -6533,10 +6533,10 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
         <v>1118.560378378698</v>
@@ -6667,16 +6667,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C32" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D32" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E32" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F32" t="n">
         <v>293.9279100914582</v>
@@ -6691,25 +6691,25 @@
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637026</v>
+        <v>61.84</v>
       </c>
       <c r="K32" t="n">
-        <v>430.9405883765121</v>
+        <v>771.3406764391787</v>
       </c>
       <c r="L32" t="n">
-        <v>415.4025075684311</v>
+        <v>1536.610676439179</v>
       </c>
       <c r="M32" t="n">
-        <v>921.0855559603649</v>
+        <v>1521.072595631097</v>
       </c>
       <c r="N32" t="n">
-        <v>1531.218651333043</v>
+        <v>1561.459999999917</v>
       </c>
       <c r="O32" t="n">
-        <v>2296.488651333084</v>
+        <v>2326.729999999959</v>
       </c>
       <c r="P32" t="n">
-        <v>3061.758651333125</v>
+        <v>3092</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6736,7 +6736,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y32" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="33">
@@ -6767,28 +6767,28 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>71.63058051381563</v>
+        <v>61.84</v>
       </c>
       <c r="J33" t="n">
-        <v>195.5871006891146</v>
+        <v>312.3286282495399</v>
       </c>
       <c r="K33" t="n">
-        <v>384.779916783498</v>
+        <v>789.6114443439233</v>
       </c>
       <c r="L33" t="n">
-        <v>656.1303783786981</v>
+        <v>1060.961905939123</v>
       </c>
       <c r="M33" t="n">
-        <v>742.2109201215574</v>
+        <v>1147.042447681983</v>
       </c>
       <c r="N33" t="n">
-        <v>1163.581204729126</v>
+        <v>1280.322732289551</v>
       </c>
       <c r="O33" t="n">
-        <v>1402.623656412844</v>
+        <v>1519.36518397327</v>
       </c>
       <c r="P33" t="n">
-        <v>1515.153000882351</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I34" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630726</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630726</v>
+        <v>877.945350542037</v>
       </c>
       <c r="N34" t="n">
-        <v>1011.831843630726</v>
+        <v>877.945350542037</v>
       </c>
       <c r="O34" t="n">
-        <v>1011.831843630726</v>
+        <v>524.9700332905068</v>
       </c>
       <c r="P34" t="n">
-        <v>941.0737317239891</v>
+        <v>124.5176117467921</v>
       </c>
       <c r="Q34" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6931,46 +6931,46 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>430.9405883765124</v>
+        <v>1155.056868702881</v>
       </c>
       <c r="L35" t="n">
-        <v>415.4025075684315</v>
+        <v>1920.326868702881</v>
       </c>
       <c r="M35" t="n">
-        <v>921.0855559603651</v>
+        <v>2426.009917094815</v>
       </c>
       <c r="N35" t="n">
-        <v>1531.218651333044</v>
+        <v>3036.143012467493</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533197</v>
+        <v>3092</v>
       </c>
       <c r="P35" t="n">
-        <v>2660.033647533245</v>
+        <v>3076.461919191918</v>
       </c>
       <c r="Q35" t="n">
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S35" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T35" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U35" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V35" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W35" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X35" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y35" t="n">
         <v>997.0248446907499</v>
@@ -7004,19 +7004,19 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>134.974877967565</v>
+        <v>71.63058051381563</v>
       </c>
       <c r="J36" t="n">
-        <v>258.9313981428639</v>
+        <v>195.5871006891146</v>
       </c>
       <c r="K36" t="n">
-        <v>448.1242142372473</v>
+        <v>384.779916783498</v>
       </c>
       <c r="L36" t="n">
-        <v>719.4746758324475</v>
+        <v>656.1303783786981</v>
       </c>
       <c r="M36" t="n">
-        <v>805.5552175753068</v>
+        <v>742.2109201215574</v>
       </c>
       <c r="N36" t="n">
         <v>1163.581204729126</v>
@@ -7062,55 +7062,55 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I37" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="Q37" t="n">
-        <v>572.6002613826477</v>
+        <v>573.9365734181883</v>
       </c>
       <c r="R37" t="n">
-        <v>132.5981119067375</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7128,10 +7128,10 @@
         <v>435.5391829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>478.6599739669322</v>
+        <v>478.6599739669085</v>
       </c>
       <c r="Y37" t="n">
-        <v>482.1592746459644</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H38" t="n">
         <v>61.84</v>
@@ -7168,19 +7168,19 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>1154.134391781985</v>
+        <v>430.0181114556213</v>
       </c>
       <c r="L38" t="n">
-        <v>1420.156760757421</v>
+        <v>794.4855845766601</v>
       </c>
       <c r="M38" t="n">
-        <v>1925.839809149355</v>
+        <v>1300.168632968594</v>
       </c>
       <c r="N38" t="n">
-        <v>1910.301728341273</v>
+        <v>1910.301728341272</v>
       </c>
       <c r="O38" t="n">
-        <v>1894.763647533191</v>
+        <v>2675.571728341328</v>
       </c>
       <c r="P38" t="n">
         <v>2660.033647533246</v>
@@ -7244,22 +7244,22 @@
         <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>483.6771006891146</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>672.869916783498</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>944.220378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M39" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N39" t="n">
-        <v>1163.581204729126</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O39" t="n">
-        <v>1402.623656412844</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P39" t="n">
         <v>1515.153000882351</v>
@@ -7299,55 +7299,55 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122601</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306959</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>509.5077622556959</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E40" t="n">
-        <v>519.4266664671089</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590444</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459297</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053273</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I40" t="n">
-        <v>756.2036690414102</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693862</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P40" t="n">
-        <v>611.3794220870153</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q40" t="n">
-        <v>172.1478398389365</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R40" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7359,16 +7359,16 @@
         <v>280.6468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>371.5582646830647</v>
+        <v>371.5582646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>435.5391829427422</v>
+        <v>435.5391829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>478.6599739669357</v>
+        <v>478.6599739669085</v>
       </c>
       <c r="Y40" t="n">
-        <v>482.159274645968</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>603.3968675156625</v>
+        <v>445.4047560890853</v>
       </c>
       <c r="C41" t="n">
-        <v>364.533657169204</v>
+        <v>255.6679077858706</v>
       </c>
       <c r="D41" t="n">
         <v>255.6679077858706</v>
@@ -7402,52 +7402,52 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>771.5463663478683</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M41" t="n">
-        <v>1282.395195076803</v>
+        <v>2438.974308114459</v>
       </c>
       <c r="N41" t="n">
-        <v>1895.615514851567</v>
+        <v>3052.194627889222</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="P41" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3092</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>2807.304881007754</v>
+        <v>2769.043670070084</v>
       </c>
       <c r="T41" t="n">
-        <v>2429.854798453649</v>
+        <v>2391.593587515979</v>
       </c>
       <c r="U41" t="n">
-        <v>1989.227226182325</v>
+        <v>1950.966015244655</v>
       </c>
       <c r="V41" t="n">
-        <v>1989.227226182325</v>
+        <v>1529.904374672105</v>
       </c>
       <c r="W41" t="n">
-        <v>1559.557048423793</v>
+        <v>1100.234196913573</v>
       </c>
       <c r="X41" t="n">
-        <v>1176.444085332209</v>
+        <v>717.1212338219889</v>
       </c>
       <c r="Y41" t="n">
-        <v>875.1133452485661</v>
+        <v>717.1212338219889</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>845.0520685412207</v>
+        <v>724.6802633024114</v>
       </c>
       <c r="C42" t="n">
-        <v>695.4561973841305</v>
+        <v>575.0843921453212</v>
       </c>
       <c r="D42" t="n">
-        <v>559.1555035480673</v>
+        <v>438.7836983092579</v>
       </c>
       <c r="E42" t="n">
-        <v>428.1735871622969</v>
+        <v>307.8017819234876</v>
       </c>
       <c r="F42" t="n">
-        <v>300.2581908614112</v>
+        <v>179.8863856226019</v>
       </c>
       <c r="G42" t="n">
-        <v>186.379871795727</v>
+        <v>66.00806655691771</v>
       </c>
       <c r="H42" t="n">
         <v>66.00806655691771</v>
@@ -7487,46 +7487,46 @@
         <v>796.7293362696823</v>
       </c>
       <c r="L42" t="n">
-        <v>1112.362177951784</v>
+        <v>1278.949797864882</v>
       </c>
       <c r="M42" t="n">
-        <v>1409.312719694643</v>
+        <v>1575.900339607742</v>
       </c>
       <c r="N42" t="n">
-        <v>1753.463004302211</v>
+        <v>1920.05062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2203.37545598593</v>
+        <v>2369.963075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>2526.774800455436</v>
+        <v>2679.025784148866</v>
       </c>
       <c r="Q42" t="n">
-        <v>2566.296328015861</v>
+        <v>2679.025784148866</v>
       </c>
       <c r="R42" t="n">
-        <v>2480.230476522543</v>
+        <v>2341.375483853533</v>
       </c>
       <c r="S42" t="n">
-        <v>2224.105224033037</v>
+        <v>2103.733418794227</v>
       </c>
       <c r="T42" t="n">
-        <v>2029.804451086053</v>
+        <v>1909.432645847244</v>
       </c>
       <c r="U42" t="n">
-        <v>1840.703077590915</v>
+        <v>1720.331272352106</v>
       </c>
       <c r="V42" t="n">
-        <v>1637.156949114632</v>
+        <v>1516.785143875823</v>
       </c>
       <c r="W42" t="n">
-        <v>1415.567915872381</v>
+        <v>1295.196110633571</v>
       </c>
       <c r="X42" t="n">
-        <v>1206.615653806333</v>
+        <v>1086.243848567523</v>
       </c>
       <c r="Y42" t="n">
-        <v>1018.341519699126</v>
+        <v>897.969714460317</v>
       </c>
     </row>
     <row r="43">
@@ -7557,43 +7557,43 @@
         <v>61.84</v>
       </c>
       <c r="I43" t="n">
-        <v>97.84287893608291</v>
+        <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>273.7966195885342</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="K43" t="n">
-        <v>273.7966195885342</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="L43" t="n">
-        <v>273.7966195885342</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="M43" t="n">
-        <v>273.7966195885342</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="N43" t="n">
-        <v>273.7966195885342</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="O43" t="n">
-        <v>273.7966195885342</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="P43" t="n">
-        <v>74.64124708689393</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="Q43" t="n">
-        <v>74.64124708689393</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="R43" t="n">
-        <v>74.64124708689393</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="S43" t="n">
-        <v>74.64124708689393</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="T43" t="n">
-        <v>77.58692624569879</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="U43" t="n">
-        <v>77.58692624569879</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="V43" t="n">
         <v>91.27831913164476</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1193.036323392743</v>
+        <v>991.066662501746</v>
       </c>
       <c r="C44" t="n">
-        <v>927.9104867836578</v>
+        <v>725.9408258926612</v>
       </c>
       <c r="D44" t="n">
-        <v>702.3153799757288</v>
+        <v>500.3457190847322</v>
       </c>
       <c r="E44" t="n">
-        <v>702.3153799757288</v>
+        <v>280.7868406939558</v>
       </c>
       <c r="F44" t="n">
-        <v>482.224845927232</v>
+        <v>280.7868406939558</v>
       </c>
       <c r="G44" t="n">
-        <v>263.2780052332762</v>
+        <v>61.84</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,22 +7639,22 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K44" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>1282.395195076803</v>
+        <v>1274.910585172492</v>
       </c>
       <c r="N44" t="n">
-        <v>1895.615514851567</v>
+        <v>1888.130904947255</v>
       </c>
       <c r="O44" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947255</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7666,25 +7666,25 @@
         <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>2781.042254745129</v>
+        <v>3092</v>
       </c>
       <c r="T44" t="n">
-        <v>2377.329545928397</v>
+        <v>2688.287291183269</v>
       </c>
       <c r="U44" t="n">
-        <v>2377.329545928397</v>
+        <v>2688.287291183269</v>
       </c>
       <c r="V44" t="n">
-        <v>1930.005279093222</v>
+        <v>2240.963024348093</v>
       </c>
       <c r="W44" t="n">
-        <v>1930.005279093222</v>
+        <v>1785.030220326934</v>
       </c>
       <c r="X44" t="n">
-        <v>1520.629689739012</v>
+        <v>1375.654630972724</v>
       </c>
       <c r="Y44" t="n">
-        <v>1193.036323392743</v>
+        <v>1048.061264626455</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>389.656180796251</v>
+        <v>1028.890452379605</v>
       </c>
       <c r="C45" t="n">
-        <v>389.656180796251</v>
+        <v>853.031954959888</v>
       </c>
       <c r="D45" t="n">
-        <v>389.656180796251</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="E45" t="n">
-        <v>232.4116381478544</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="F45" t="n">
-        <v>232.4116381478544</v>
+        <v>379.04606964929</v>
       </c>
       <c r="G45" t="n">
-        <v>92.27069281954398</v>
+        <v>238.9051243209795</v>
       </c>
       <c r="H45" t="n">
         <v>92.27069281954398</v>
@@ -7727,43 +7727,43 @@
         <v>1201.729797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1373.148353424001</v>
+        <v>1306.631021998729</v>
       </c>
       <c r="N45" t="n">
-        <v>1691.55863803157</v>
+        <v>1625.041306606297</v>
       </c>
       <c r="O45" t="n">
-        <v>2115.731089715289</v>
+        <v>2049.213758290016</v>
       </c>
       <c r="P45" t="n">
-        <v>2413.390434184796</v>
+        <v>2346.873102759523</v>
       </c>
       <c r="Q45" t="n">
-        <v>2427.171961745221</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="R45" t="n">
-        <v>2063.259035187262</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="S45" t="n">
-        <v>1780.871156435129</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="T45" t="n">
-        <v>1560.307757225519</v>
+        <v>2140.091231110338</v>
       </c>
       <c r="U45" t="n">
-        <v>1344.943757467755</v>
+        <v>1924.727231352574</v>
       </c>
       <c r="V45" t="n">
-        <v>1115.135002728846</v>
+        <v>1694.918476613664</v>
       </c>
       <c r="W45" t="n">
-        <v>867.2833432239684</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="X45" t="n">
-        <v>632.0684548952941</v>
+        <v>1442.979290169969</v>
       </c>
       <c r="Y45" t="n">
-        <v>417.5316945254614</v>
+        <v>1228.442529800137</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="C46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="D46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="E46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="F46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="G46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="H46" t="n">
         <v>61.84</v>
       </c>
       <c r="I46" t="n">
-        <v>61.84</v>
+        <v>72.10287893608292</v>
       </c>
       <c r="J46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="K46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="L46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="M46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="N46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="O46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="P46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="R46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="S46" t="n">
-        <v>61.84</v>
+        <v>143.672759546362</v>
       </c>
       <c r="T46" t="n">
-        <v>61.84</v>
+        <v>120.4156216612533</v>
       </c>
       <c r="U46" t="n">
-        <v>61.84</v>
+        <v>156.0968142995399</v>
       </c>
       <c r="V46" t="n">
-        <v>61.84</v>
+        <v>143.8035716568973</v>
       </c>
       <c r="W46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="X46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="Y46" t="n">
-        <v>61.84</v>
+        <v>104.0330566683016</v>
       </c>
     </row>
   </sheetData>
@@ -7967,22 +7967,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>649.655890836063</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>273.1022858719847</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8207,19 +8207,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>597.9703808667776</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>582.6427212635809</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P5" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8441,13 +8441,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>500.8454983898776</v>
       </c>
       <c r="L8" t="n">
-        <v>726.8100877168811</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
@@ -8459,7 +8459,7 @@
         <v>814.2870600406815</v>
       </c>
       <c r="Q8" t="n">
-        <v>189.0212843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,10 +8681,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
@@ -8693,7 +8693,7 @@
         <v>884.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>137.6925874496847</v>
+        <v>435.68366954167</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>51.7013460871449</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,10 +8927,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>51.70134608714521</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,10 +9164,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>114.0702823596368</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9389,10 +9389,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>16.65833984205487</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9404,7 +9404,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>814.2870600406815</v>
+        <v>114.0702823596368</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9626,16 +9626,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>240.811073919941</v>
       </c>
       <c r="L23" t="n">
-        <v>435.3966095009885</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O23" t="n">
         <v>70.24786957409245</v>
@@ -9866,22 +9866,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>802.8493095354884</v>
+        <v>110.4553161506355</v>
       </c>
       <c r="P26" t="n">
-        <v>773.2870600407081</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,22 +10100,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>601.3242207078167</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>440.4259272085471</v>
+        <v>843.2478695741272</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407163</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>50.42570624509119</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>532.6151883949684</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741336</v>
+        <v>843.2478695741345</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407226</v>
+        <v>773.2870600407235</v>
       </c>
       <c r="Q32" t="n">
-        <v>218.1443195076926</v>
+        <v>188.2053843274865</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,10 +10574,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,13 +10586,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>445.5401158122453</v>
+        <v>140.9289872312756</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407299</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>203.5880843274875</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,22 +10811,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>277.8315931340005</v>
+        <v>375.292246238141</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>843.247869574149</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407372</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,13 +11060,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>835.6876575496134</v>
+        <v>110.4553161506355</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
@@ -11291,16 +11291,16 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>657.4491031847087</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>835.6876575496134</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407599</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>29.21007785422267</v>
+        <v>29.21007785422597</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>5.66244969644525</v>
+        <v>5.662449696452683</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785422734</v>
+        <v>29.21007785422415</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23229,10 +23229,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>148.3645116136913</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,13 +23271,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>124.815409821719</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23429,10 +23429,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>160.8253284926234</v>
+        <v>298.1988081954788</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23463,22 +23463,22 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>86.30994672070052</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>82.66357762404179</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23618,19 +23618,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>36.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>29.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>23.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -23645,13 +23645,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>37.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>172.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>269.6316114025499</v>
+        <v>210.1611065479036</v>
       </c>
       <c r="N16" t="n">
         <v>320.1850752716849</v>
@@ -23660,16 +23660,16 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>382.7066165981673</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
         <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>111.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>36.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23760,7 +23760,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4306086145857648</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -23897,13 +23897,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>108.2004986247733</v>
+        <v>69.8091295274528</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4306086145859922</v>
+        <v>0.430608614525994</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -24119,7 +24119,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>144.5476281577792</v>
@@ -24134,13 +24134,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>69.04626797189974</v>
+        <v>117.7212724259164</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.430608614585708</v>
+        <v>0.4306086145172685</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24338,7 +24338,7 @@
         <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24356,28 +24356,28 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>361.445564079015</v>
+        <v>265.0706617671527</v>
       </c>
       <c r="P25" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>108.2004986247733</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,10 +24411,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>218.0725611011333</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
@@ -24423,10 +24423,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24465,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>399.159430424472</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24596,13 +24596,13 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>153.4024400718014</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.408275783157251</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24645,25 +24645,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>205.3667782497391</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,13 +24696,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>35.06290239760591</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>229.6316114025499</v>
@@ -25079,16 +25079,16 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>326.3973665406075</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>372.7884307962738</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25322,13 +25322,13 @@
         <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.322948915208713</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.322948915185336</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25556,16 +25556,16 @@
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>397.7708462434594</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,10 +25596,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>48.63509842281132</v>
       </c>
       <c r="D41" t="n">
-        <v>89.5620638503497</v>
+        <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>191.3632896068686</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -25653,7 +25653,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25662,7 +25662,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>298.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25690,7 +25690,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>119.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>249.0686043139941</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>18.29835555589847</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25793,7 +25793,7 @@
         <v>427.445564079015</v>
       </c>
       <c r="P43" t="n">
-        <v>277.2840785516536</v>
+        <v>474.4478973282775</v>
       </c>
       <c r="Q43" t="n">
         <v>512.839266425598</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>238.5746568521125</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25839,16 +25839,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>21.58603352258399</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25893,7 +25893,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>451.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -25909,25 +25909,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>169.9597980544084</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>174.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>145.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>228.816087775958</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26042,16 +26042,16 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5070656.91139658</v>
+        <v>5070656.911396583</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5771671.607130159</v>
+        <v>5771671.607130164</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6407332.814361461</v>
+        <v>6407332.814361467</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7047516.909673573</v>
+        <v>7047516.909673578</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7754188.614377987</v>
+        <v>7754188.614377992</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8459154.198562099</v>
+        <v>8459154.198562102</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9164119.782746214</v>
+        <v>9164119.782746216</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9783489.805831028</v>
+        <v>9783489.805831036</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10362789.6995931</v>
+        <v>10362789.69959311</v>
       </c>
     </row>
   </sheetData>
@@ -26281,37 +26281,37 @@
         <v>1323084.101908757</v>
       </c>
       <c r="F2" t="n">
-        <v>1377041.660956641</v>
+        <v>1377041.660956642</v>
       </c>
       <c r="G2" t="n">
-        <v>1432508.291281669</v>
+        <v>1432508.29128167</v>
       </c>
       <c r="H2" t="n">
-        <v>1432508.29128167</v>
+        <v>1432508.291281675</v>
       </c>
       <c r="I2" t="n">
-        <v>1432508.291281669</v>
+        <v>1432508.291281675</v>
       </c>
       <c r="J2" t="n">
         <v>1308202.281724756</v>
       </c>
       <c r="K2" t="n">
-        <v>1308202.281724756</v>
+        <v>1308202.281724757</v>
       </c>
       <c r="L2" t="n">
         <v>1440581.845941442</v>
       </c>
       <c r="M2" t="n">
-        <v>1440581.845941442</v>
+        <v>1440581.845941441</v>
       </c>
       <c r="N2" t="n">
-        <v>1440581.845941442</v>
+        <v>1440581.845941441</v>
       </c>
       <c r="O2" t="n">
         <v>1269155.597801759</v>
       </c>
       <c r="P2" t="n">
-        <v>1183786.739426839</v>
+        <v>1183786.73942684</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614247.571579208</v>
+        <v>619095.9472656922</v>
       </c>
       <c r="C4" t="n">
-        <v>612495.6628399484</v>
+        <v>617344.0385264326</v>
       </c>
       <c r="D4" t="n">
-        <v>610741.3775271376</v>
+        <v>615589.7532136219</v>
       </c>
       <c r="E4" t="n">
-        <v>532123.6038252711</v>
+        <v>536922.2846154375</v>
       </c>
       <c r="F4" t="n">
-        <v>556398.2196192667</v>
+        <v>561196.9004094332</v>
       </c>
       <c r="G4" t="n">
-        <v>581187.6277435899</v>
+        <v>585986.3085337563</v>
       </c>
       <c r="H4" t="n">
-        <v>579514.6928034928</v>
+        <v>584313.3735936618</v>
       </c>
       <c r="I4" t="n">
-        <v>577839.422419066</v>
+        <v>582638.1032092355</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524998.4738086243</v>
       </c>
       <c r="K4" t="n">
-        <v>518858.3176303694</v>
+        <v>523533.7321546826</v>
       </c>
       <c r="L4" t="n">
-        <v>581043.8351797324</v>
+        <v>585765.7481143256</v>
       </c>
       <c r="M4" t="n">
-        <v>579313.7164781799</v>
+        <v>584035.6294127728</v>
       </c>
       <c r="N4" t="n">
-        <v>577581.1101536278</v>
+        <v>582303.0230882207</v>
       </c>
       <c r="O4" t="n">
-        <v>494869.5309141541</v>
+        <v>499544.9454384673</v>
       </c>
       <c r="P4" t="n">
-        <v>454063.7935190182</v>
+        <v>458739.2080433314</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495049.9266161022</v>
+        <v>490201.5509296178</v>
       </c>
       <c r="C6" t="n">
-        <v>783329.8353553612</v>
+        <v>778481.4596688771</v>
       </c>
       <c r="D6" t="n">
-        <v>785084.1206681724</v>
+        <v>780235.7449816882</v>
       </c>
       <c r="E6" t="n">
-        <v>542553.7730834855</v>
+        <v>537755.0922933194</v>
       </c>
       <c r="F6" t="n">
-        <v>729250.9223373743</v>
+        <v>724452.2415472085</v>
       </c>
       <c r="G6" t="n">
-        <v>755974.2125380795</v>
+        <v>751175.5317479138</v>
       </c>
       <c r="H6" t="n">
-        <v>780047.1474781769</v>
+        <v>775248.4666880132</v>
       </c>
       <c r="I6" t="n">
-        <v>781722.4178626034</v>
+        <v>776923.7370724397</v>
       </c>
       <c r="J6" t="n">
-        <v>313069.2974404451</v>
+        <v>308393.8829161318</v>
       </c>
       <c r="K6" t="n">
-        <v>702630.0390943869</v>
+        <v>697954.6245700743</v>
       </c>
       <c r="L6" t="n">
-        <v>712875.5317617098</v>
+        <v>708153.6188271162</v>
       </c>
       <c r="M6" t="n">
-        <v>789805.6504632616</v>
+        <v>785083.7375286685</v>
       </c>
       <c r="N6" t="n">
-        <v>791538.256787814</v>
+        <v>786816.3438532206</v>
       </c>
       <c r="O6" t="n">
-        <v>634980.9698876046</v>
+        <v>630305.5553632914</v>
       </c>
       <c r="P6" t="n">
-        <v>667003.642907821</v>
+        <v>662328.2283835083</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>157.3092074428802</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>56.5117682972699</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27496,13 +27496,13 @@
         <v>400</v>
       </c>
       <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>400</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>99.03700384580283</v>
+        <v>91.56884869434688</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27609,13 +27609,13 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="I4" t="n">
-        <v>349.3048867337101</v>
-      </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27648,7 +27648,7 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>155.8027094679971</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27682,7 +27682,7 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>400</v>
@@ -27718,13 +27718,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>56.51176829727007</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>307.3903671255649</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>172.5204020740694</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27797,16 +27797,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>342.2743756165772</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>399.7554761955677</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27837,10 +27837,10 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27888,7 +27888,7 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>245.1678924788697</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>307.3903671255648</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27922,11 +27922,11 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
+        <v>307.3903671255648</v>
+      </c>
+      <c r="H8" t="n">
         <v>400</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -27958,10 +27958,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27973,7 +27973,7 @@
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28034,7 +28034,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>303.3742880620964</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>342.2743756165772</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28068,10 +28068,10 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
@@ -28086,7 +28086,7 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>211.3914053801886</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28128,13 +28128,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>295.8364148149685</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28247,7 +28247,7 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>19.11687125883891</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>19.11687125883863</v>
+        <v>225</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28487,25 +28487,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>251</v>
-      </c>
-      <c r="L15" t="n">
-        <v>166.1982915220774</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="O15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>244.1190264315978</v>
       </c>
       <c r="Q15" t="n">
-        <v>251</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28730,10 +28730,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>261.5913251766235</v>
       </c>
       <c r="N18" t="n">
-        <v>155.6705902671032</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28867,7 +28867,7 @@
         <v>279</v>
       </c>
       <c r="F20" t="n">
-        <v>279</v>
+        <v>279.000000000006</v>
       </c>
       <c r="G20" t="n">
         <v>279</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283496</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -28955,20 +28955,20 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
+        <v>261.5913251766234</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>279</v>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>279</v>
       </c>
-      <c r="K21" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283643</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29192,7 +29192,7 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>279</v>
+        <v>261.5913251766235</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29201,7 +29201,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>155.6705902671031</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>279</v>
@@ -29210,13 +29210,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29435,7 +29435,7 @@
         <v>225</v>
       </c>
       <c r="K27" t="n">
-        <v>225</v>
+        <v>19.11687125883918</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
@@ -29444,7 +29444,7 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
@@ -29669,13 +29669,13 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>19.11687125883917</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M30" t="n">
         <v>225</v>
@@ -29815,7 +29815,7 @@
         <v>291</v>
       </c>
       <c r="F32" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="G32" t="n">
         <v>291</v>
@@ -29872,7 +29872,7 @@
         <v>291</v>
       </c>
       <c r="Y32" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="33">
@@ -29903,13 +29903,13 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
-        <v>227.015861157829</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>127.8102101760009</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -29918,7 +29918,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>291</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="C34" t="n">
         <v>291</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>291</v>
@@ -30109,7 +30109,7 @@
         <v>291</v>
       </c>
       <c r="Y35" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="36">
@@ -30140,22 +30140,22 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
+        <v>227.015861157829</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>291</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>227.0158611578289</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -30264,7 +30264,7 @@
         <v>291</v>
       </c>
       <c r="X37" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="Y37" t="n">
         <v>291</v>
@@ -30277,7 +30277,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="C38" t="n">
         <v>291</v>
@@ -30295,7 +30295,7 @@
         <v>291</v>
       </c>
       <c r="H38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30380,7 +30380,7 @@
         <v>291</v>
       </c>
       <c r="J39" t="n">
-        <v>227.015861157829</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30398,7 +30398,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="Q39" t="n">
         <v>291</v>
@@ -30495,7 +30495,7 @@
         <v>291</v>
       </c>
       <c r="V40" t="n">
-        <v>291.0000000000276</v>
+        <v>291</v>
       </c>
       <c r="W40" t="n">
         <v>291</v>
@@ -30623,7 +30623,7 @@
         <v>213</v>
       </c>
       <c r="L42" t="n">
-        <v>44.72967685545576</v>
+        <v>213</v>
       </c>
       <c r="M42" t="n">
         <v>213</v>
@@ -30635,10 +30635,10 @@
         <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>213</v>
+        <v>198.5185492730614</v>
       </c>
       <c r="Q42" t="n">
-        <v>213</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
         <v>213</v>
@@ -30693,10 +30693,10 @@
         <v>213</v>
       </c>
       <c r="I43" t="n">
-        <v>213</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>213</v>
+        <v>65.00462472645802</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30726,13 +30726,13 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>213</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
-        <v>213</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30863,7 +30863,7 @@
         <v>187</v>
       </c>
       <c r="M45" t="n">
-        <v>86.20001395581806</v>
+        <v>19.01079029392637</v>
       </c>
       <c r="N45" t="n">
         <v>187</v>
@@ -30930,10 +30930,10 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>176.6334556201183</v>
+        <v>187</v>
       </c>
       <c r="J46" t="n">
-        <v>35.26894883590776</v>
+        <v>107.5617575331594</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>150.9583912744579</v>
+        <v>187</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34746,7 +34746,7 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -34895,13 +34895,13 @@
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>172.6714311135918</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34934,7 +34934,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>4.844318193539124</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>112.6416758584891</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35123,10 +35123,10 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
@@ -35138,10 +35138,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
         <v>189.9754334937423</v>
@@ -35174,7 +35174,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>45.99758226265348</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35354,10 +35354,10 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
@@ -35372,7 +35372,7 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>34.75794976007029</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35414,13 +35414,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.371061965506158</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35460,10 +35460,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
@@ -35472,7 +35472,7 @@
         <v>814</v>
       </c>
       <c r="P11" t="n">
-        <v>137.4055274090032</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35533,7 +35533,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965146</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>132.7828757734918</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>16.65833984205456</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,10 +35706,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35773,25 +35773,25 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>442.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>440.2896668707643</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>113.6660045146532</v>
+        <v>357.785030946251</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>16.65833984205488</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,10 +35943,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P17" t="n">
-        <v>113.7832223189554</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36016,10 +36016,10 @@
         <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>86.95004216450428</v>
+        <v>348.5413673411278</v>
       </c>
       <c r="N18" t="n">
-        <v>290.297140375758</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
         <v>241.4570219027464</v>
@@ -36028,7 +36028,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36168,10 +36168,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>16.65833984205487</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36183,13 +36183,13 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>814</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.512089101654111e-11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36241,19 +36241,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>61.87361410865147</v>
+        <v>44.46493928527486</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>346.7744449078945</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M21" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N21" t="n">
         <v>134.6265501086548</v>
@@ -36265,7 +36265,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36405,16 +36405,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>240.811073919941</v>
       </c>
       <c r="L23" t="n">
-        <v>435.3966095009885</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36426,7 +36426,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.981979528761874e-11</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>61.87361410865147</v>
+        <v>44.46493928527492</v>
       </c>
       <c r="J24" t="n">
         <v>125.2086062376757</v>
@@ -36487,7 +36487,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>429.7619656157901</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
         <v>365.9500421645043</v>
@@ -36496,13 +36496,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36645,22 +36645,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>732.601439961396</v>
+        <v>40.20744657654306</v>
       </c>
       <c r="P26" t="n">
-        <v>773.0000000000266</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36721,7 +36721,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996305</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
@@ -36730,7 +36730,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
@@ -36879,22 +36879,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>57.06209306549945</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>370.1780576344547</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,13 +36955,13 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M30" t="n">
         <v>311.9500421645043</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320763039</v>
+        <v>727.1079320760052</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>773.0000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,13 +37189,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>9.889475266480432</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>253.0188164136766</v>
       </c>
       <c r="K33" t="n">
-        <v>191.1038546407913</v>
+        <v>482.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>274.091375348687</v>
@@ -37204,7 +37204,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>425.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>117.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.886199662945266</v>
+        <v>3.886199662921342</v>
       </c>
       <c r="C34" t="n">
         <v>18.27475335195533</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320762842</v>
+        <v>727.1079320760053</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>73.87361410865147</v>
+        <v>9.889475266480432</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37441,7 +37441,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
-        <v>361.6424112664837</v>
+        <v>425.6265501086548</v>
       </c>
       <c r="O36" t="n">
         <v>241.4570219027464</v>
@@ -37550,7 +37550,7 @@
         <v>64.62719016129032</v>
       </c>
       <c r="X37" t="n">
-        <v>43.55635456991639</v>
+        <v>43.55635456989245</v>
       </c>
       <c r="Y37" t="n">
         <v>3.534647150537637</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
-        <v>773.0000000000002</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>727.1079320762924</v>
+        <v>727.1079320760048</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>352.2244673955047</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37684,7 +37684,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>340.6818656724819</v>
       </c>
       <c r="Q39" t="n">
         <v>117.9207349095204</v>
@@ -37781,7 +37781,7 @@
         <v>140.0416087255421</v>
       </c>
       <c r="V40" t="n">
-        <v>91.82968978381136</v>
+        <v>91.82968978378381</v>
       </c>
       <c r="W40" t="n">
         <v>64.62719016129032</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,13 +37839,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>765.439787975521</v>
+        <v>40.20744657654306</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>404.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>318.8210522041427</v>
+        <v>487.091375348687</v>
       </c>
       <c r="M42" t="n">
         <v>299.9500421645043</v>
@@ -37921,10 +37921,10 @@
         <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>326.6660045146532</v>
+        <v>312.1845537877145</v>
       </c>
       <c r="Q42" t="n">
-        <v>39.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>36.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>177.7310511640922</v>
+        <v>29.73567589055027</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38012,13 +38012,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.975433493742287</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>13.82968978378381</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
@@ -38070,16 +38070,16 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>113.1869755423914</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>765.439787975521</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>773.0000000000784</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38149,7 +38149,7 @@
         <v>461.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>173.1500561203223</v>
+        <v>105.9608324584307</v>
       </c>
       <c r="N45" t="n">
         <v>321.6265501086548</v>
@@ -38216,10 +38216,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>10.36654437988173</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>72.29280869725164</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>36.04160872554206</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
